--- a/public/download/member_bulk_demo.xlsx
+++ b/public/download/member_bulk_demo.xlsx
@@ -1,104 +1,318 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xml:space="preserve">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="9045"/>
+    <workbookView activeTab="0" autoFilterDateGrouping="true" firstSheet="0" minimized="false" showHorizontalScroll="true" showSheetTabs="true" showVerticalScroll="true" tabRatio="600" visibility="visible"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="Members" sheetId="1" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <definedNames/>
+  <calcPr calcId="999999" calcMode="auto" calcCompleted="1" fullCalcOnLoad="0" forceFullCalc="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="19">
-  <si>
-    <t>first_name</t>
-  </si>
-  <si>
-    <t>last_name</t>
-  </si>
-  <si>
-    <t>email</t>
-  </si>
-  <si>
-    <t>gender</t>
-  </si>
-  <si>
-    <t>date_of_birth</t>
-  </si>
-  <si>
-    <t>mobile</t>
-  </si>
-  <si>
-    <t>on_behalf</t>
-  </si>
-  <si>
-    <t>package</t>
-  </si>
-  <si>
-    <t>password</t>
-  </si>
-  <si>
-    <t>Mr.Demo</t>
-  </si>
-  <si>
-    <t>Member</t>
-  </si>
-  <si>
-    <t>demomember@gmail.com</t>
-  </si>
-  <si>
-    <t>1996-02-22</t>
-  </si>
-  <si>
-    <t>1995-04-15</t>
-  </si>
-  <si>
-    <t>Mr.</t>
-  </si>
-  <si>
-    <t>Tom</t>
-  </si>
-  <si>
-    <t>mrtom@gmail.com</t>
-  </si>
-  <si>
-    <t>+8801234567859</t>
-  </si>
-  <si>
-    <t>+8801745222222</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="91">
+  <si>
+    <t>Candidate Mobile No</t>
+  </si>
+  <si>
+    <t>Email Address</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>Introduction</t>
+  </si>
+  <si>
+    <t>First Name</t>
+  </si>
+  <si>
+    <t>Last Name</t>
+  </si>
+  <si>
+    <t>Gender</t>
+  </si>
+  <si>
+    <t>Date Of Birth</t>
+  </si>
+  <si>
+    <t>On Behalf</t>
+  </si>
+  <si>
+    <t>Package</t>
+  </si>
+  <si>
+    <t>Marital Status</t>
+  </si>
+  <si>
+    <t>Number Of Children</t>
+  </si>
+  <si>
+    <t>Height Ft</t>
+  </si>
+  <si>
+    <t>Height Inch</t>
+  </si>
+  <si>
+    <t>Weight</t>
+  </si>
+  <si>
+    <t>Disability (If Any)</t>
+  </si>
+  <si>
+    <t>Present Address Country</t>
+  </si>
+  <si>
+    <t>Present Address State</t>
+  </si>
+  <si>
+    <t>Present Address City</t>
+  </si>
+  <si>
+    <t>Permanent Address Country</t>
+  </si>
+  <si>
+    <t>Permanent Address State</t>
+  </si>
+  <si>
+    <t>Permanent Address City</t>
+  </si>
+  <si>
+    <t>Degree</t>
+  </si>
+  <si>
+    <t>Specialization</t>
+  </si>
+  <si>
+    <t>Institution</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Role / Nature</t>
+  </si>
+  <si>
+    <t>Company / Business</t>
+  </si>
+  <si>
+    <t>Currency</t>
+  </si>
+  <si>
+    <t>Monthly Income</t>
+  </si>
+  <si>
+    <t>Yearly Income</t>
+  </si>
+  <si>
+    <t>Mother Tongue</t>
+  </si>
+  <si>
+    <t>Known Languages</t>
+  </si>
+  <si>
+    <t>Caste</t>
+  </si>
+  <si>
+    <t>Follower of (Sect)</t>
+  </si>
+  <si>
+    <t>Name of the Mandal</t>
+  </si>
+  <si>
+    <t>Nitya Pooja Daily</t>
+  </si>
+  <si>
+    <t>Wear Kanthi</t>
+  </si>
+  <si>
+    <t>Eat Onion / Garlic</t>
+  </si>
+  <si>
+    <t>Perform Aarti / Ghar Sabha</t>
+  </si>
+  <si>
+    <t>Observe Sampradaya Fasts</t>
+  </si>
+  <si>
+    <t>Temple Visit Frequency</t>
+  </si>
+  <si>
+    <t>Volunteer Activities</t>
+  </si>
+  <si>
+    <t>Define Yourself As Satsangi</t>
+  </si>
+  <si>
+    <t>Diet</t>
+  </si>
+  <si>
+    <t>Drink</t>
+  </si>
+  <si>
+    <t>Smoke</t>
+  </si>
+  <si>
+    <t>Living With</t>
+  </si>
+  <si>
+    <t>Time Of Birth</t>
+  </si>
+  <si>
+    <t>City Of Birth</t>
+  </si>
+  <si>
+    <t>Moon Sign</t>
+  </si>
+  <si>
+    <t>Father</t>
+  </si>
+  <si>
+    <t>Father Occupation</t>
+  </si>
+  <si>
+    <t>Mother</t>
+  </si>
+  <si>
+    <t>Mother Occupation</t>
+  </si>
+  <si>
+    <t>jane.doe@example.com</t>
+  </si>
+  <si>
+    <t>ChangeMe123</t>
+  </si>
+  <si>
+    <t>A brief introduction about the candidate.</t>
+  </si>
+  <si>
+    <t>Jane</t>
+  </si>
+  <si>
+    <t>Doe</t>
+  </si>
+  <si>
+    <t>Female</t>
+  </si>
+  <si>
+    <t>1998-05-14</t>
+  </si>
+  <si>
+    <t>Daughter</t>
+  </si>
+  <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>Never Married</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Gujarat</t>
+  </si>
+  <si>
+    <t>Ahmedabad</t>
+  </si>
+  <si>
+    <t>Bachelor of Commerce (B.Com)</t>
+  </si>
+  <si>
+    <t>Finance</t>
+  </si>
+  <si>
+    <t>Gujarat University</t>
+  </si>
+  <si>
+    <t>Job</t>
+  </si>
+  <si>
+    <t>Software Engineer</t>
+  </si>
+  <si>
+    <t>Acme Pvt Ltd</t>
+  </si>
+  <si>
+    <t>INR</t>
+  </si>
+  <si>
+    <t>Gujarati</t>
+  </si>
+  <si>
+    <t>Gujarati, Hindi, English</t>
+  </si>
+  <si>
+    <t>Lohana</t>
+  </si>
+  <si>
+    <t>BAPS</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Once a week</t>
+  </si>
+  <si>
+    <t>Swaminarayan Food (No Onion No Garlic)</t>
+  </si>
+  <si>
+    <t>no</t>
+  </si>
+  <si>
+    <t>With Parents</t>
+  </si>
+  <si>
+    <t>10:30 AM</t>
+  </si>
+  <si>
+    <t>taurus</t>
+  </si>
+  <si>
+    <t>Ramesh Doe</t>
+  </si>
+  <si>
+    <t>Business</t>
+  </si>
+  <si>
+    <t>Sita Doe</t>
+  </si>
+  <si>
+    <t>Homemaker</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xml:space="preserve">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
+      <b val="0"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <b val="1"/>
+      <i val="0"/>
+      <strike val="0"/>
+      <u val="none"/>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-      <family val="1"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -118,41 +332,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+  <cellXfs count="2">
+    <xf xfId="0" fontId="0" numFmtId="0" fillId="0" borderId="0" applyFont="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
+    <xf xfId="0" fontId="1" numFmtId="0" fillId="0" borderId="0" applyFont="1" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleMedium9"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <tableStyles defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotTableStyle1"/>
 </styleSheet>
 </file>
 
@@ -199,7 +390,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -234,7 +425,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -442,20 +633,71 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xml:space="preserve" mc:Ignorable="x14ac">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+  </sheetPr>
+  <dimension ref="A1:BC2"/>
+  <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="20.7109375" customWidth="1"/>
-    <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="3" width="30.7109375" customWidth="1"/>
-    <col min="4" max="4" width="10.7109375" customWidth="1"/>
-    <col min="5" max="6" width="15.7109375" customWidth="1"/>
-    <col min="7" max="8" width="10.7109375" customWidth="1"/>
-    <col min="9" max="9" width="15.7109375" customWidth="1"/>
+    <col min="1" max="1" width="20" customWidth="true" style="0"/>
+    <col min="2" max="2" width="20" customWidth="true" style="0"/>
+    <col min="3" max="3" width="20" customWidth="true" style="0"/>
+    <col min="4" max="4" width="20" customWidth="true" style="0"/>
+    <col min="5" max="5" width="20" customWidth="true" style="0"/>
+    <col min="6" max="6" width="20" customWidth="true" style="0"/>
+    <col min="7" max="7" width="20" customWidth="true" style="0"/>
+    <col min="8" max="8" width="20" customWidth="true" style="0"/>
+    <col min="9" max="9" width="20" customWidth="true" style="0"/>
+    <col min="10" max="10" width="20" customWidth="true" style="0"/>
+    <col min="11" max="11" width="20" customWidth="true" style="0"/>
+    <col min="12" max="12" width="20" customWidth="true" style="0"/>
+    <col min="13" max="13" width="20" customWidth="true" style="0"/>
+    <col min="14" max="14" width="20" customWidth="true" style="0"/>
+    <col min="15" max="15" width="20" customWidth="true" style="0"/>
+    <col min="16" max="16" width="20" customWidth="true" style="0"/>
+    <col min="17" max="17" width="20" customWidth="true" style="0"/>
+    <col min="18" max="18" width="20" customWidth="true" style="0"/>
+    <col min="19" max="19" width="20" customWidth="true" style="0"/>
+    <col min="20" max="20" width="20" customWidth="true" style="0"/>
+    <col min="21" max="21" width="20" customWidth="true" style="0"/>
+    <col min="22" max="22" width="20" customWidth="true" style="0"/>
+    <col min="23" max="23" width="20" customWidth="true" style="0"/>
+    <col min="24" max="24" width="20" customWidth="true" style="0"/>
+    <col min="25" max="25" width="20" customWidth="true" style="0"/>
+    <col min="26" max="26" width="20" customWidth="true" style="0"/>
+    <col min="27" max="27" width="20" customWidth="true" style="0"/>
+    <col min="28" max="28" width="20" customWidth="true" style="0"/>
+    <col min="29" max="29" width="20" customWidth="true" style="0"/>
+    <col min="30" max="30" width="20" customWidth="true" style="0"/>
+    <col min="31" max="31" width="20" customWidth="true" style="0"/>
+    <col min="32" max="32" width="20" customWidth="true" style="0"/>
+    <col min="33" max="33" width="20" customWidth="true" style="0"/>
+    <col min="34" max="34" width="20" customWidth="true" style="0"/>
+    <col min="35" max="35" width="20" customWidth="true" style="0"/>
+    <col min="36" max="36" width="20" customWidth="true" style="0"/>
+    <col min="37" max="37" width="20" customWidth="true" style="0"/>
+    <col min="38" max="38" width="20" customWidth="true" style="0"/>
+    <col min="39" max="39" width="20" customWidth="true" style="0"/>
+    <col min="40" max="40" width="20" customWidth="true" style="0"/>
+    <col min="41" max="41" width="20" customWidth="true" style="0"/>
+    <col min="42" max="42" width="20" customWidth="true" style="0"/>
+    <col min="43" max="43" width="20" customWidth="true" style="0"/>
+    <col min="44" max="44" width="20" customWidth="true" style="0"/>
+    <col min="45" max="45" width="20" customWidth="true" style="0"/>
+    <col min="46" max="46" width="20" customWidth="true" style="0"/>
+    <col min="47" max="47" width="20" customWidth="true" style="0"/>
+    <col min="48" max="48" width="20" customWidth="true" style="0"/>
+    <col min="49" max="49" width="20" customWidth="true" style="0"/>
+    <col min="50" max="50" width="20" customWidth="true" style="0"/>
+    <col min="51" max="51" width="20" customWidth="true" style="0"/>
+    <col min="52" max="52" width="20" customWidth="true" style="0"/>
+    <col min="53" max="53" width="20" customWidth="true" style="0"/>
+    <col min="54" max="54" width="20" customWidth="true" style="0"/>
+    <col min="55" max="55" width="20" customWidth="true" style="0"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:55">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -483,80 +725,309 @@
       <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AK1" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AL1" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AM1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AN1" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="AT1" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="AU1" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="AV1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="AW1" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="AX1" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="AY1" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="AZ1" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="BA1" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="BB1" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="BC1" s="1" t="s">
+        <v>54</v>
+      </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>9</v>
+    <row r="2" spans="1:55">
+      <c r="A2">
+        <v>9876543210</v>
       </c>
       <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" s="3">
-        <v>1</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>12</v>
-      </c>
-      <c r="F2" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="G2" s="3">
-        <v>1</v>
-      </c>
-      <c r="H2" s="3">
-        <v>1</v>
-      </c>
-      <c r="I2" s="3">
-        <v>1234</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="3">
-        <v>2</v>
-      </c>
-      <c r="E3" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="G3" s="3">
-        <v>2</v>
-      </c>
-      <c r="H3" s="3">
+        <v>55</v>
+      </c>
+      <c r="C2" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" t="s">
+        <v>57</v>
+      </c>
+      <c r="E2" t="s">
+        <v>58</v>
+      </c>
+      <c r="F2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G2" t="s">
+        <v>60</v>
+      </c>
+      <c r="H2" t="s">
+        <v>61</v>
+      </c>
+      <c r="I2" t="s">
+        <v>62</v>
+      </c>
+      <c r="J2" t="s">
+        <v>63</v>
+      </c>
+      <c r="K2" t="s">
+        <v>64</v>
+      </c>
+      <c r="M2">
+        <v>5</v>
+      </c>
+      <c r="N2">
         <v>4</v>
       </c>
-      <c r="I3" s="3">
-        <v>1234</v>
+      <c r="O2">
+        <v>55</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>65</v>
+      </c>
+      <c r="R2" t="s">
+        <v>66</v>
+      </c>
+      <c r="S2" t="s">
+        <v>67</v>
+      </c>
+      <c r="T2" t="s">
+        <v>65</v>
+      </c>
+      <c r="U2" t="s">
+        <v>66</v>
+      </c>
+      <c r="V2" t="s">
+        <v>67</v>
+      </c>
+      <c r="W2" t="s">
+        <v>68</v>
+      </c>
+      <c r="X2" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>70</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>71</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>72</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>73</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>74</v>
+      </c>
+      <c r="AD2">
+        <v>50000</v>
+      </c>
+      <c r="AE2">
+        <v>600000</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>75</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>76</v>
+      </c>
+      <c r="AH2" t="s">
+        <v>77</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>78</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AL2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>80</v>
+      </c>
+      <c r="AN2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AO2" t="s">
+        <v>79</v>
+      </c>
+      <c r="AP2" t="s">
+        <v>81</v>
+      </c>
+      <c r="AS2" t="s">
+        <v>82</v>
+      </c>
+      <c r="AT2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AU2" t="s">
+        <v>83</v>
+      </c>
+      <c r="AV2" t="s">
+        <v>84</v>
+      </c>
+      <c r="AW2" t="s">
+        <v>85</v>
+      </c>
+      <c r="AX2" t="s">
+        <v>67</v>
+      </c>
+      <c r="AY2" t="s">
+        <v>86</v>
+      </c>
+      <c r="AZ2" t="s">
+        <v>87</v>
+      </c>
+      <c r="BA2" t="s">
+        <v>88</v>
+      </c>
+      <c r="BB2" t="s">
+        <v>89</v>
+      </c>
+      <c r="BC2" t="s">
+        <v>90</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="C2" r:id="rId1"/>
-    <hyperlink ref="C3" r:id="rId2"/>
-  </hyperlinks>
+  <printOptions gridLines="false" gridLinesSet="true"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="1" orientation="default" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver"/>
+  <headerFooter differentOddEven="false" differentFirst="false" scaleWithDoc="true" alignWithMargins="true">
+    <oddHeader/>
+    <oddFooter/>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <tableParts count="0"/>
 </worksheet>
 </file>